--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2014/COLORADO_2014.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2014/COLORADO_2014.xlsx
@@ -2850,7 +2850,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Temosachi</t>
+          <t>Temosachic</t>
         </is>
       </c>
       <c r="C139">
@@ -5802,7 +5802,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C303">
@@ -5964,7 +5964,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C312">
@@ -13110,7 +13110,7 @@
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C709">
@@ -14640,7 +14640,7 @@
       </c>
       <c r="B794" t="inlineStr">
         <is>
-          <t>San Pedro Totolapa</t>
+          <t>San Pedro Totolapam</t>
         </is>
       </c>
       <c r="C794">
@@ -22272,7 +22272,7 @@
       </c>
       <c r="B1218" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C1218">
